--- a/recapitulare/_11D_Unitatea_1.xlsx
+++ b/recapitulare/_11D_Unitatea_1.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Recapitulare-clasa-a-11a\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Competente Digitale\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D20D4811-55D8-49E3-B2C1-3699A1DDFFA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59354871-E1CE-444F-A830-1046D040056A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Materii si note" sheetId="1" r:id="rId1"/>
     <sheet name="Tabla inmultirii cu 6" sheetId="2" r:id="rId2"/>
     <sheet name="Timp la televizor" sheetId="3" r:id="rId3"/>
-    <sheet name="Functii" sheetId="4" r:id="rId4"/>
+    <sheet name="Functii de baza" sheetId="4" r:id="rId4"/>
     <sheet name="Diagrama medii" sheetId="5" r:id="rId5"/>
     <sheet name="Diagrama Viteza Automobil" sheetId="6" r:id="rId6"/>
     <sheet name="Diagrama cresterii populatiei" sheetId="7" r:id="rId7"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="142">
   <si>
     <t>MATERIA</t>
   </si>
@@ -834,6 +834,24 @@
       </rPr>
       <t>Dan a înregistrat într‑un tabel poziția automobilului în care se afla față de</t>
     </r>
+  </si>
+  <si>
+    <t>Nota 1</t>
+  </si>
+  <si>
+    <t>Nota 2</t>
+  </si>
+  <si>
+    <t>ABS</t>
+  </si>
+  <si>
+    <t>INT</t>
+  </si>
+  <si>
+    <t>SQRT</t>
+  </si>
+  <si>
+    <t>ROUND</t>
   </si>
 </sst>
 </file>
@@ -1063,7 +1081,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1094,6 +1112,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1107,7 +1137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1137,6 +1167,8 @@
     <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="28" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3196,15 +3228,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>21960</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>19800</xdr:rowOff>
+      <xdr:colOff>269610</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>124575</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3223,8 +3255,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="2275920"/>
-          <a:ext cx="5019480" cy="2133000"/>
+          <a:off x="247650" y="2695575"/>
+          <a:ext cx="4755885" cy="2124825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3925,7 +3957,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="17">
-        <f>SUM(B2:H2)</f>
+        <f t="shared" ref="I2:I11" si="0">SUM(B2:H2)</f>
         <v>368</v>
       </c>
     </row>
@@ -3955,7 +3987,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="17">
-        <f>SUM(B3:H3)</f>
+        <f t="shared" si="0"/>
         <v>150</v>
       </c>
     </row>
@@ -3985,7 +4017,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="17">
-        <f>SUM(B4:H4)</f>
+        <f t="shared" si="0"/>
         <v>189</v>
       </c>
     </row>
@@ -4015,7 +4047,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="17">
-        <f>SUM(B5:H5)</f>
+        <f t="shared" si="0"/>
         <v>252</v>
       </c>
     </row>
@@ -4045,7 +4077,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="17">
-        <f>SUM(B6:H6)</f>
+        <f t="shared" si="0"/>
         <v>266</v>
       </c>
     </row>
@@ -4075,7 +4107,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="17">
-        <f>SUM(B7:H7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4105,7 +4137,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="17">
-        <f>SUM(B8:H8)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4135,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="17">
-        <f>SUM(B9:H9)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4165,7 +4197,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="17">
-        <f>SUM(B10:H10)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4195,7 +4227,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="17">
-        <f>SUM(B11:H11)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4452,129 +4484,383 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>81</v>
       </c>
       <c r="B1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D1" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="E1" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="F1" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="G1" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="I1" s="17" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>84</v>
       </c>
       <c r="B2">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="C2" s="17" t="str">
-        <f>IF(B2&gt;=5,"Promovat","Respins")</f>
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+      <c r="D2" s="30">
+        <f>AVERAGE(B2:C2)</f>
+        <v>10</v>
+      </c>
+      <c r="E2" s="30">
+        <f>ABS(D2)</f>
+        <v>10</v>
+      </c>
+      <c r="F2" s="30">
+        <f>INT(D2)</f>
+        <v>10</v>
+      </c>
+      <c r="G2" s="30">
+        <f>SQRT(D2)</f>
+        <v>3.1622776601683795</v>
+      </c>
+      <c r="H2" s="30">
+        <f>ROUND(G2,2)</f>
+        <v>3.16</v>
+      </c>
+      <c r="I2" s="17" t="str">
+        <f>IF(D2&gt;=5,"Promovat","Respins")</f>
         <v>Promovat</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>85</v>
       </c>
       <c r="B3">
-        <v>4.75</v>
-      </c>
-      <c r="C3" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>9</v>
+      </c>
+      <c r="D3" s="30">
+        <f t="shared" ref="D3:D11" si="0">AVERAGE(B3:C3)</f>
+        <v>9</v>
+      </c>
+      <c r="E3" s="30">
+        <f t="shared" ref="E3:E11" si="1">ABS(D3)</f>
+        <v>9</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F11" si="2">INT(D3)</f>
+        <v>9</v>
+      </c>
+      <c r="G3" s="30">
+        <f t="shared" ref="G3:G11" si="3">SQRT(D3)</f>
+        <v>3</v>
+      </c>
+      <c r="H3" s="30">
+        <f t="shared" ref="H3:H11" si="4">ROUND(G3,2)</f>
+        <v>3</v>
+      </c>
+      <c r="I3" s="17" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>87</v>
       </c>
       <c r="B4">
-        <v>7.1</v>
-      </c>
-      <c r="C4" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>8</v>
+      </c>
+      <c r="D4" s="30">
+        <f t="shared" si="0"/>
+        <v>5.5</v>
+      </c>
+      <c r="E4" s="30">
+        <f t="shared" si="1"/>
+        <v>5.5</v>
+      </c>
+      <c r="F4" s="30">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="G4" s="30">
+        <f t="shared" si="3"/>
+        <v>2.3452078799117149</v>
+      </c>
+      <c r="H4" s="30">
+        <f t="shared" si="4"/>
+        <v>2.35</v>
+      </c>
+      <c r="I4" s="17" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>89</v>
       </c>
       <c r="B5">
-        <v>3.9</v>
-      </c>
-      <c r="C5" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+      <c r="D5" s="30">
+        <f t="shared" si="0"/>
+        <v>7.5</v>
+      </c>
+      <c r="E5" s="30">
+        <f t="shared" si="1"/>
+        <v>7.5</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="G5" s="30">
+        <f t="shared" si="3"/>
+        <v>2.7386127875258306</v>
+      </c>
+      <c r="H5" s="30">
+        <f t="shared" si="4"/>
+        <v>2.74</v>
+      </c>
+      <c r="I5" s="17" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>91</v>
       </c>
       <c r="B6">
-        <v>10</v>
-      </c>
-      <c r="C6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6" s="30">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="E6" s="30">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="G6" s="30">
+        <f t="shared" si="3"/>
+        <v>2.4494897427831779</v>
+      </c>
+      <c r="H6" s="30">
+        <f t="shared" si="4"/>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="I6" s="17" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>93</v>
       </c>
       <c r="B7">
+        <v>7</v>
+      </c>
+      <c r="C7">
         <v>5</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="D7" s="30">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="E7" s="30">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="F7" s="30">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="G7" s="30">
+        <f t="shared" si="3"/>
+        <v>2.4494897427831779</v>
+      </c>
+      <c r="H7" s="30">
+        <f t="shared" si="4"/>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="I7" s="17" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>95</v>
       </c>
       <c r="B8">
-        <v>4.99</v>
-      </c>
-      <c r="C8" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8" s="30">
+        <f t="shared" si="0"/>
+        <v>5.5</v>
+      </c>
+      <c r="E8" s="30">
+        <f t="shared" si="1"/>
+        <v>5.5</v>
+      </c>
+      <c r="F8" s="30">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="G8" s="30">
+        <f t="shared" si="3"/>
+        <v>2.3452078799117149</v>
+      </c>
+      <c r="H8" s="30">
+        <f t="shared" si="4"/>
+        <v>2.35</v>
+      </c>
+      <c r="I8" s="17" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
         <v>97</v>
       </c>
       <c r="B9">
-        <v>8.4499999999999993</v>
-      </c>
-      <c r="C9" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9" s="30">
+        <f t="shared" si="0"/>
+        <v>5.5</v>
+      </c>
+      <c r="E9" s="30">
+        <f t="shared" si="1"/>
+        <v>5.5</v>
+      </c>
+      <c r="F9" s="30">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="G9" s="30">
+        <f t="shared" si="3"/>
+        <v>2.3452078799117149</v>
+      </c>
+      <c r="H9" s="30">
+        <f t="shared" si="4"/>
+        <v>2.35</v>
+      </c>
+      <c r="I9" s="17" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
         <v>99</v>
       </c>
       <c r="B10">
-        <v>2.5</v>
-      </c>
-      <c r="C10" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10" s="30">
+        <f t="shared" si="0"/>
+        <v>5.5</v>
+      </c>
+      <c r="E10" s="30">
+        <f t="shared" si="1"/>
+        <v>5.5</v>
+      </c>
+      <c r="F10" s="30">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="G10" s="30">
+        <f t="shared" si="3"/>
+        <v>2.3452078799117149</v>
+      </c>
+      <c r="H10" s="30">
+        <f t="shared" si="4"/>
+        <v>2.35</v>
+      </c>
+      <c r="I10" s="17" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
         <v>101</v>
       </c>
       <c r="B11">
-        <v>6.3</v>
-      </c>
-      <c r="C11" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" s="30">
+        <f t="shared" si="0"/>
+        <v>5.5</v>
+      </c>
+      <c r="E11" s="30">
+        <f t="shared" si="1"/>
+        <v>5.5</v>
+      </c>
+      <c r="F11" s="30">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="G11" s="30">
+        <f t="shared" si="3"/>
+        <v>2.3452078799117149</v>
+      </c>
+      <c r="H11" s="30">
+        <f t="shared" si="4"/>
+        <v>2.35</v>
+      </c>
+      <c r="I11" s="17" t="s">
         <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="D12">
+        <f>SUM(D2:D11)</f>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -4768,34 +5054,34 @@
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75"/>
   <sheetData>
     <row r="1" spans="1:10" ht="23.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="23">
+      <c r="B1" s="29">
         <v>0</v>
       </c>
-      <c r="C1" s="23">
+      <c r="C1" s="29">
         <v>1</v>
       </c>
-      <c r="D1" s="23">
+      <c r="D1" s="29">
         <v>2</v>
       </c>
-      <c r="E1" s="23">
+      <c r="E1" s="29">
         <v>3</v>
       </c>
-      <c r="F1" s="23">
+      <c r="F1" s="29">
         <v>4</v>
       </c>
-      <c r="G1" s="23">
+      <c r="G1" s="29">
         <v>5</v>
       </c>
-      <c r="H1" s="23">
+      <c r="H1" s="29">
         <v>6</v>
       </c>
-      <c r="I1" s="23">
+      <c r="I1" s="29">
         <v>7</v>
       </c>
-      <c r="J1" s="23">
+      <c r="J1" s="29">
         <v>8</v>
       </c>
     </row>
